--- a/referee_response/time_to_departure/benchmark_gradeA_tables_fy.xlsx
+++ b/referee_response/time_to_departure/benchmark_gradeA_tables_fy.xlsx
@@ -115,7 +115,7 @@
     <t xml:space="preserve">Interaction Specification: Peer- and Benchmark-Adjusted Returns by Benchmark Confidence</t>
   </si>
   <si>
-    <t xml:space="preserve">This table repeats the interaction specification of xsec_interactions_fye1.xlsx (all Table III controls, fiscal-year fixed effects instead of fiscal-year-end date fixed effects, Conflicted CIO interacted with X). Panel A uses Peer-Adjusted Return, for all plan-years and for the plan-years that also have the grade-A benchmark-adjusted return; Panel B uses Benchmark-Adjusted Return for three versions of the policy benchmark. Benchmark-Adjusted Return is the plan's return minus its policy benchmark return. 'Reported + inferred grade A/B' uses the benchmark return reported in the plan's financial report or, where none is stated, an inferred value graded A or B (the version in the earlier tables). 'Reported + inferred grade A only' drops the inferred values graded B (28 plan-years, 10 of them conflicted). 'Reported benchmarks only' drops all inferred values. For binary X, Conflicted CIO is the effect when X = 0 and the italic row gives the effect when X = 1. Continuous X (log pay, relative pay filled within spell, log CIO age) is centered at its regression-sample mean, so Conflicted CIO is the effect at average X, and the italic rows give the effect at the 25th and 75th percentiles. Log CIO Age is the paper's log_cio_age, ln(1 + age); that column drops the lagged log CIO age control. The standard errors are double clustered by plan and year. Coefficients marked with ***, **, and * are significant at the 1%, 5%, and 10% level, respectively.</t>
+    <t xml:space="preserve">This table repeats the interaction specification of xsec_interactions_fye1.xlsx (all Table III controls, fiscal-year fixed effects instead of fiscal-year-end date fixed effects, Conflicted CIO interacted with X). Panel A uses Peer-Adjusted Return, for all plan-years and for the plan-years that also have the grade-A benchmark-adjusted return; Panel B uses Benchmark-Adjusted Return for three versions of the policy benchmark. Benchmark-Adjusted Return is the plan's return minus its policy benchmark return. 'Reported + inferred grade A/B' uses the benchmark return reported in the plan's financial report or, where none is stated, an inferred value graded A or B (the version in the earlier tables). 'Reported + inferred grade A only' drops the inferred values graded B (28 plan-years, 10 of them conflicted). 'Reported benchmarks only' drops all inferred values. For binary X, Conflicted CIO is the effect when X = 0 and the italic row gives the effect when X = 1. Continuous X (log pay, relative pay filled within spell, standardized log CIO age) is centered at its regression-sample mean, so Conflicted CIO is the effect at average X, and the italic rows give the effect at the 25th and 75th percentiles. Log CIO Age (std.) is the paper's log_cio_age, ln(1 + age), standardized over the Table III sample (mean 3.950, standard deviation 0.174), so its interaction is the change in the effect of conflict for a one-standard-deviation increase in log age, about 10 years at the mean age of 52; that column drops the lagged log CIO age control. The standard errors are double clustered by plan and year. Coefficients marked with ***, **, and * are significant at the 1%, 5%, and 10% level, respectively.</t>
   </si>
   <si>
     <t xml:space="preserve">X = Underpaid</t>
@@ -142,7 +142,7 @@
     <t xml:space="preserve">X = Relative CIO Pay (filled)</t>
   </si>
   <si>
-    <t xml:space="preserve">X = Log CIO Age</t>
+    <t xml:space="preserve">X = Log CIO Age (std.)</t>
   </si>
   <si>
     <t xml:space="preserve">Conflicted CIO x X</t>
@@ -265,7 +265,7 @@
     <t xml:space="preserve">Relative CIO Pay (filled)</t>
   </si>
   <si>
-    <t xml:space="preserve">Log CIO Age</t>
+    <t xml:space="preserve">Log CIO Age (std.)</t>
   </si>
 </sst>
 </file>
@@ -1492,7 +1492,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="168" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="195.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>30</v>
       </c>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J9" s="8" t="str">
         <f aca="false">IF(Estimates!I51="","",TEXT(Estimates!E51,"0.000")&amp;IF(Estimates!I51&lt;0.01,"***",IF(Estimates!I51&lt;0.05,"**",IF(Estimates!I51&lt;0.1,"*",""))))</f>
-        <v>2.620**</v>
+        <v>0.457**</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="J11" s="8" t="str">
         <f aca="false">IF(Estimates!I60="","",TEXT(Estimates!E60,"0.000")&amp;IF(Estimates!I60&lt;0.01,"***",IF(Estimates!I60&lt;0.05,"**",IF(Estimates!I60&lt;0.1,"*",""))))</f>
-        <v>-1.096</v>
+        <v>-0.191</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="J12" s="8" t="str">
         <f aca="false">IF(Estimates!H60="","","("&amp;TEXT(Estimates!H60,"0.00")&amp;")")</f>
-        <v>(-1.70)</v>
+        <v>(-1.69)</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="J28" s="8" t="str">
         <f aca="false">IF(Estimates!I90="","",TEXT(Estimates!E90,"0.000")&amp;IF(Estimates!I90&lt;0.01,"***",IF(Estimates!I90&lt;0.05,"**",IF(Estimates!I90&lt;0.1,"*",""))))</f>
-        <v>3.081**</v>
+        <v>0.537**</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="J29" s="8" t="str">
         <f aca="false">IF(Estimates!H90="","","("&amp;TEXT(Estimates!H90,"0.00")&amp;")")</f>
-        <v>(2.60)</v>
+        <v>(2.59)</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="J30" s="8" t="str">
         <f aca="false">IF(Estimates!I99="","",TEXT(Estimates!E99,"0.000")&amp;IF(Estimates!I99&lt;0.01,"***",IF(Estimates!I99&lt;0.05,"**",IF(Estimates!I99&lt;0.1,"*",""))))</f>
-        <v>-1.250</v>
+        <v>-0.218</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="J31" s="8" t="str">
         <f aca="false">IF(Estimates!H99="","","("&amp;TEXT(Estimates!H99,"0.00")&amp;")")</f>
-        <v>(-1.68)</v>
+        <v>(-1.67)</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="J36" s="14" t="str">
         <f aca="false">IF(Estimates!H108="","","("&amp;TEXT(Estimates!H108,"0.00")&amp;")")</f>
-        <v>(-3.02)</v>
+        <v>(-3.01)</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="J48" s="8" t="str">
         <f aca="false">IF(Estimates!I129="","",TEXT(Estimates!E129,"0.000")&amp;IF(Estimates!I129&lt;0.01,"***",IF(Estimates!I129&lt;0.05,"**",IF(Estimates!I129&lt;0.1,"*",""))))</f>
-        <v>1.223*</v>
+        <v>0.213*</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="J49" s="8" t="str">
         <f aca="false">IF(Estimates!H129="","","("&amp;TEXT(Estimates!H129,"0.00")&amp;")")</f>
-        <v>(2.09)</v>
+        <v>(2.03)</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="J50" s="8" t="str">
         <f aca="false">IF(Estimates!I138="","",TEXT(Estimates!E138,"0.000")&amp;IF(Estimates!I138&lt;0.01,"***",IF(Estimates!I138&lt;0.05,"**",IF(Estimates!I138&lt;0.1,"*",""))))</f>
-        <v>-1.215**</v>
+        <v>-0.212**</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="J51" s="8" t="str">
         <f aca="false">IF(Estimates!H138="","","("&amp;TEXT(Estimates!H138,"0.00")&amp;")")</f>
-        <v>(-2.59)</v>
+        <v>(-2.50)</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="J56" s="14" t="str">
         <f aca="false">IF(Estimates!H147="","","("&amp;TEXT(Estimates!H147,"0.00")&amp;")")</f>
-        <v>(-4.30)</v>
+        <v>(-4.35)</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="J58" s="14" t="str">
         <f aca="false">IF(Estimates!H150="","","("&amp;TEXT(Estimates!H150,"0.00")&amp;")")</f>
-        <v>(-1.25)</v>
+        <v>(-1.23)</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="J66" s="8" t="str">
         <f aca="false">IF(Estimates!H159="","","("&amp;TEXT(Estimates!H159,"0.00")&amp;")")</f>
-        <v>(-2.53)</v>
+        <v>(-2.51)</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="J67" s="8" t="str">
         <f aca="false">IF(Estimates!I168="","",TEXT(Estimates!E168,"0.000")&amp;IF(Estimates!I168&lt;0.01,"***",IF(Estimates!I168&lt;0.05,"**",IF(Estimates!I168&lt;0.1,"*",""))))</f>
-        <v>1.139*</v>
+        <v>0.199*</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="J68" s="8" t="str">
         <f aca="false">IF(Estimates!H168="","","("&amp;TEXT(Estimates!H168,"0.00")&amp;")")</f>
-        <v>(1.96)</v>
+        <v>(1.89)</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="J69" s="8" t="str">
         <f aca="false">IF(Estimates!I177="","",TEXT(Estimates!E177,"0.000")&amp;IF(Estimates!I177&lt;0.01,"***",IF(Estimates!I177&lt;0.05,"**",IF(Estimates!I177&lt;0.1,"*",""))))</f>
-        <v>-1.219**</v>
+        <v>-0.213**</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="J70" s="8" t="str">
         <f aca="false">IF(Estimates!H177="","","("&amp;TEXT(Estimates!H177,"0.00")&amp;")")</f>
-        <v>(-2.56)</v>
+        <v>(-2.47)</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="J75" s="14" t="str">
         <f aca="false">IF(Estimates!H186="","","("&amp;TEXT(Estimates!H186,"0.00")&amp;")")</f>
-        <v>(-4.09)</v>
+        <v>(-4.12)</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="J77" s="14" t="str">
         <f aca="false">IF(Estimates!H189="","","("&amp;TEXT(Estimates!H189,"0.00")&amp;")")</f>
-        <v>(-1.16)</v>
+        <v>(-1.14)</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="J86" s="8" t="str">
         <f aca="false">IF(Estimates!I207="","",TEXT(Estimates!E207,"0.000")&amp;IF(Estimates!I207&lt;0.01,"***",IF(Estimates!I207&lt;0.05,"**",IF(Estimates!I207&lt;0.1,"*",""))))</f>
-        <v>0.884</v>
+        <v>0.154</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="J87" s="8" t="str">
         <f aca="false">IF(Estimates!H207="","","("&amp;TEXT(Estimates!H207,"0.00")&amp;")")</f>
-        <v>(1.58)</v>
+        <v>(1.52)</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="J88" s="8" t="str">
         <f aca="false">IF(Estimates!I216="","",TEXT(Estimates!E216,"0.000")&amp;IF(Estimates!I216&lt;0.01,"***",IF(Estimates!I216&lt;0.05,"**",IF(Estimates!I216&lt;0.1,"*",""))))</f>
-        <v>-0.920**</v>
+        <v>-0.160**</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3597,7 +3597,7 @@
       </c>
       <c r="J89" s="8" t="str">
         <f aca="false">IF(Estimates!H216="","","("&amp;TEXT(Estimates!H216,"0.00")&amp;")")</f>
-        <v>(-2.20)</v>
+        <v>(-2.13)</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="J94" s="14" t="str">
         <f aca="false">IF(Estimates!H225="","","("&amp;TEXT(Estimates!H225,"0.00")&amp;")")</f>
-        <v>(-4.02)</v>
+        <v>(-4.00)</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="J96" s="14" t="str">
         <f aca="false">IF(Estimates!H228="","","("&amp;TEXT(Estimates!H228,"0.00")&amp;")")</f>
-        <v>(-1.30)</v>
+        <v>(-1.29)</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5172,18 +5172,18 @@
         <v>-0.328589713610827</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>0.146369354269987</v>
+        <v>0.146371195922301</v>
       </c>
       <c r="G42" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H42" s="24" t="n">
         <f aca="false">IF(F42&gt;0,E42/F42,"")</f>
-        <v>-2.24493518639649</v>
+        <v>-2.24490694046972</v>
       </c>
       <c r="I42" s="24" t="n">
         <f aca="false">IF(H42="","",TDIST(ABS(H42),G42-1,2))</f>
-        <v>0.0375753690191536</v>
+        <v>0.0375774992731667</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5448,21 +5448,21 @@
         <v>40</v>
       </c>
       <c r="E51" s="22" t="n">
-        <v>2.62013064902941</v>
+        <v>0.456687924422623</v>
       </c>
       <c r="F51" s="22" t="n">
-        <v>1.01794929427392</v>
+        <v>0.177570934982612</v>
       </c>
       <c r="G51" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H51" s="24" t="n">
         <f aca="false">IF(F51&gt;0,E51/F51,"")</f>
-        <v>2.57393041457757</v>
+        <v>2.57186191235262</v>
       </c>
       <c r="I51" s="24" t="n">
         <f aca="false">IF(H51="","",TDIST(ABS(H51),G51-1,2))</f>
-        <v>0.0191175626982323</v>
+        <v>0.0192006346284145</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5727,21 +5727,21 @@
         <v>41</v>
       </c>
       <c r="E60" s="22" t="n">
-        <v>-1.0959561788428</v>
+        <v>-0.191024807392438</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>0.646389523479079</v>
+        <v>0.112872070655618</v>
       </c>
       <c r="G60" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H60" s="24" t="n">
         <f aca="false">IF(F60&gt;0,E60/F60,"")</f>
-        <v>-1.69550424169006</v>
+        <v>-1.69240101898431</v>
       </c>
       <c r="I60" s="24" t="n">
         <f aca="false">IF(H60="","",TDIST(ABS(H60),G60-1,2))</f>
-        <v>0.107207816943312</v>
+        <v>0.107806854082021</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6006,21 +6006,21 @@
         <v>43</v>
       </c>
       <c r="E69" s="22" t="n">
-        <v>-0.622739740387641</v>
+        <v>-0.62273974038764</v>
       </c>
       <c r="F69" s="22" t="n">
-        <v>0.178803433879983</v>
+        <v>0.178858648737227</v>
       </c>
       <c r="G69" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H69" s="24" t="n">
         <f aca="false">IF(F69&gt;0,E69/F69,"")</f>
-        <v>-3.4828175660521</v>
+        <v>-3.48174239705092</v>
       </c>
       <c r="I69" s="24" t="n">
         <f aca="false">IF(H69="","",TDIST(ABS(H69),G69-1,2))</f>
-        <v>0.00265613487396872</v>
+        <v>0.00266248080617203</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6099,21 +6099,21 @@
         <v>44</v>
       </c>
       <c r="E72" s="22" t="n">
-        <v>-0.0269486455728279</v>
+        <v>-0.0269486455728278</v>
       </c>
       <c r="F72" s="22" t="n">
-        <v>0.194255084445043</v>
+        <v>0.194318117010551</v>
       </c>
       <c r="G72" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H72" s="24" t="n">
         <f aca="false">IF(F72&gt;0,E72/F72,"")</f>
-        <v>-0.138728134966537</v>
+        <v>-0.138683134580624</v>
       </c>
       <c r="I72" s="24" t="n">
         <f aca="false">IF(H72="","",TDIST(ABS(H72),G72-1,2))</f>
-        <v>0.891205268097507</v>
+        <v>0.891240320680824</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6381,18 +6381,18 @@
         <v>-0.298201316339029</v>
       </c>
       <c r="F81" s="22" t="n">
-        <v>0.154800843616822</v>
+        <v>0.154757069494161</v>
       </c>
       <c r="G81" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H81" s="24" t="n">
         <f aca="false">IF(F81&gt;0,E81/F81,"")</f>
-        <v>-1.92635459453416</v>
+        <v>-1.92689947744378</v>
       </c>
       <c r="I81" s="24" t="n">
         <f aca="false">IF(H81="","",TDIST(ABS(H81),G81-1,2))</f>
-        <v>0.07000098898093</v>
+        <v>0.0699287659904468</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6657,21 +6657,21 @@
         <v>40</v>
       </c>
       <c r="E90" s="22" t="n">
-        <v>3.08145624286035</v>
+        <v>0.537096826172516</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>1.18678535421333</v>
+        <v>0.207219583512742</v>
       </c>
       <c r="G90" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H90" s="24" t="n">
         <f aca="false">IF(F90&gt;0,E90/F90,"")</f>
-        <v>2.59647309593142</v>
+        <v>2.59192117399217</v>
       </c>
       <c r="I90" s="24" t="n">
         <f aca="false">IF(H90="","",TDIST(ABS(H90),G90-1,2))</f>
-        <v>0.0182340484697947</v>
+        <v>0.0184092713050241</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6936,21 +6936,21 @@
         <v>41</v>
       </c>
       <c r="E99" s="22" t="n">
-        <v>-1.25015789052392</v>
+        <v>-0.217902115848853</v>
       </c>
       <c r="F99" s="22" t="n">
-        <v>0.743839385649753</v>
+        <v>0.130689933470742</v>
       </c>
       <c r="G99" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H99" s="24" t="n">
         <f aca="false">IF(F99&gt;0,E99/F99,"")</f>
-        <v>-1.68068257024585</v>
+        <v>-1.66732134650322</v>
       </c>
       <c r="I99" s="24" t="n">
         <f aca="false">IF(H99="","",TDIST(ABS(H99),G99-1,2))</f>
-        <v>0.110094930632351</v>
+        <v>0.112754414138329</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7218,18 +7218,18 @@
         <v>-0.63568784681973</v>
       </c>
       <c r="F108" s="22" t="n">
-        <v>0.21070423804593</v>
+        <v>0.21134605211694</v>
       </c>
       <c r="G108" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H108" s="24" t="n">
         <f aca="false">IF(F108&gt;0,E108/F108,"")</f>
-        <v>-3.01696754044957</v>
+        <v>-3.00780563654909</v>
       </c>
       <c r="I108" s="24" t="n">
         <f aca="false">IF(H108="","",TDIST(ABS(H108),G108-1,2))</f>
-        <v>0.00740686203894809</v>
+        <v>0.00755602882949823</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7311,18 +7311,18 @@
         <v>0.065004001977121</v>
       </c>
       <c r="F111" s="22" t="n">
-        <v>0.199305617153452</v>
+        <v>0.198836068580069</v>
       </c>
       <c r="G111" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H111" s="24" t="n">
         <f aca="false">IF(F111&gt;0,E111/F111,"")</f>
-        <v>0.326152382986136</v>
+        <v>0.326922587241483</v>
       </c>
       <c r="I111" s="24" t="n">
         <f aca="false">IF(H111="","",TDIST(ABS(H111),G111-1,2))</f>
-        <v>0.74807048006356</v>
+        <v>0.74749748711766</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7587,21 +7587,21 @@
         <v>10</v>
       </c>
       <c r="E120" s="22" t="n">
-        <v>-0.370903892075184</v>
+        <v>-0.370903892075183</v>
       </c>
       <c r="F120" s="22" t="n">
-        <v>0.136278449481173</v>
+        <v>0.13659526218145</v>
       </c>
       <c r="G120" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H120" s="24" t="n">
         <f aca="false">IF(F120&gt;0,E120/F120,"")</f>
-        <v>-2.72166210789201</v>
+        <v>-2.71534961133926</v>
       </c>
       <c r="I120" s="24" t="n">
         <f aca="false">IF(H120="","",TDIST(ABS(H120),G120-1,2))</f>
-        <v>0.0139922329200139</v>
+        <v>0.014181407943359</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7866,21 +7866,21 @@
         <v>40</v>
       </c>
       <c r="E129" s="22" t="n">
-        <v>1.22278685290306</v>
+        <v>0.213131352847018</v>
       </c>
       <c r="F129" s="22" t="n">
-        <v>0.585050378476718</v>
+        <v>0.105235719620924</v>
       </c>
       <c r="G129" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H129" s="24" t="n">
         <f aca="false">IF(F129&gt;0,E129/F129,"")</f>
-        <v>2.09005394729733</v>
+        <v>2.02527576772176</v>
       </c>
       <c r="I129" s="24" t="n">
         <f aca="false">IF(H129="","",TDIST(ABS(H129),G129-1,2))</f>
-        <v>0.0510750979719304</v>
+        <v>0.0579293331930968</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8145,21 +8145,21 @@
         <v>41</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>-1.21517942390365</v>
+        <v>-0.211805380433687</v>
       </c>
       <c r="F138" s="22" t="n">
-        <v>0.468693214487872</v>
+        <v>0.0847393094319077</v>
       </c>
       <c r="G138" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H138" s="24" t="n">
         <f aca="false">IF(F138&gt;0,E138/F138,"")</f>
-        <v>-2.59269685658121</v>
+        <v>-2.49949382233146</v>
       </c>
       <c r="I138" s="24" t="n">
         <f aca="false">IF(H138="","",TDIST(ABS(H138),G138-1,2))</f>
-        <v>0.0183792995126905</v>
+        <v>0.0223315034070536</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8427,18 +8427,18 @@
         <v>-0.504923921396851</v>
       </c>
       <c r="F147" s="22" t="n">
-        <v>0.117466624264153</v>
+        <v>0.116081877836135</v>
       </c>
       <c r="G147" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H147" s="24" t="n">
         <f aca="false">IF(F147&gt;0,E147/F147,"")</f>
-        <v>-4.29844583139978</v>
+        <v>-4.34972220306101</v>
       </c>
       <c r="I147" s="24" t="n">
         <f aca="false">IF(H147="","",TDIST(ABS(H147),G147-1,2))</f>
-        <v>0.000432585132618365</v>
+        <v>0.000386124304330427</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8517,21 +8517,21 @@
         <v>44</v>
       </c>
       <c r="E150" s="22" t="n">
-        <v>-0.226874611876294</v>
+        <v>-0.226874611876293</v>
       </c>
       <c r="F150" s="22" t="n">
-        <v>0.181299106284925</v>
+        <v>0.184369497072217</v>
       </c>
       <c r="G150" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H150" s="24" t="n">
         <f aca="false">IF(F150&gt;0,E150/F150,"")</f>
-        <v>-1.25138295783844</v>
+        <v>-1.23054309676523</v>
       </c>
       <c r="I150" s="24" t="n">
         <f aca="false">IF(H150="","",TDIST(ABS(H150),G150-1,2))</f>
-        <v>0.226814648822966</v>
+        <v>0.234332935254145</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8799,18 +8799,18 @@
         <v>-0.349171046460651</v>
       </c>
       <c r="F159" s="22" t="n">
-        <v>0.138185686608926</v>
+        <v>0.1388573163402</v>
       </c>
       <c r="G159" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H159" s="24" t="n">
         <f aca="false">IF(F159&gt;0,E159/F159,"")</f>
-        <v>-2.52682499200389</v>
+        <v>-2.51460316001775</v>
       </c>
       <c r="I159" s="24" t="n">
         <f aca="false">IF(H159="","",TDIST(ABS(H159),G159-1,2))</f>
-        <v>0.0210963095416531</v>
+        <v>0.0216404713580099</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9075,21 +9075,21 @@
         <v>40</v>
       </c>
       <c r="E168" s="22" t="n">
-        <v>1.13892124080796</v>
+        <v>0.198513603792278</v>
       </c>
       <c r="F168" s="22" t="n">
-        <v>0.580305353699914</v>
+        <v>0.104907486092415</v>
       </c>
       <c r="G168" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H168" s="24" t="n">
         <f aca="false">IF(F168&gt;0,E168/F168,"")</f>
-        <v>1.96262404533479</v>
+        <v>1.89227300344803</v>
       </c>
       <c r="I168" s="24" t="n">
         <f aca="false">IF(H168="","",TDIST(ABS(H168),G168-1,2))</f>
-        <v>0.0653360129697859</v>
+        <v>0.074652331287171</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9354,21 +9354,21 @@
         <v>41</v>
       </c>
       <c r="E177" s="22" t="n">
-        <v>-1.21924237620046</v>
+        <v>-0.212513551704515</v>
       </c>
       <c r="F177" s="22" t="n">
-        <v>0.475648064780492</v>
+        <v>0.0859532429116905</v>
       </c>
       <c r="G177" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H177" s="24" t="n">
         <f aca="false">IF(F177&gt;0,E177/F177,"")</f>
-        <v>-2.5633287854606</v>
+        <v>-2.47243203985746</v>
       </c>
       <c r="I177" s="24" t="n">
         <f aca="false">IF(H177="","",TDIST(ABS(H177),G177-1,2))</f>
-        <v>0.0195469564388887</v>
+        <v>0.0236214304418259</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9633,21 +9633,21 @@
         <v>43</v>
       </c>
       <c r="E186" s="22" t="n">
-        <v>-0.473907712425528</v>
+        <v>-0.473907712425527</v>
       </c>
       <c r="F186" s="22" t="n">
-        <v>0.115916961287898</v>
+        <v>0.114945783120023</v>
       </c>
       <c r="G186" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H186" s="24" t="n">
         <f aca="false">IF(F186&gt;0,E186/F186,"")</f>
-        <v>-4.08833795468897</v>
+        <v>-4.12288036639574</v>
       </c>
       <c r="I186" s="24" t="n">
         <f aca="false">IF(H186="","",TDIST(ABS(H186),G186-1,2))</f>
-        <v>0.000689892282863588</v>
+        <v>0.000638862861312808</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9729,18 +9729,18 @@
         <v>-0.214928591204918</v>
       </c>
       <c r="F189" s="22" t="n">
-        <v>0.184961443750177</v>
+        <v>0.188472655691625</v>
       </c>
       <c r="G189" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H189" s="24" t="n">
         <f aca="false">IF(F189&gt;0,E189/F189,"")</f>
-        <v>-1.16201834743038</v>
+        <v>-1.14037015298697</v>
       </c>
       <c r="I189" s="24" t="n">
         <f aca="false">IF(H189="","",TDIST(ABS(H189),G189-1,2))</f>
-        <v>0.260404698170455</v>
+        <v>0.269079052708731</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10005,21 +10005,21 @@
         <v>10</v>
       </c>
       <c r="E198" s="22" t="n">
-        <v>-0.343086171735109</v>
+        <v>-0.343086171735108</v>
       </c>
       <c r="F198" s="22" t="n">
-        <v>0.133909878431354</v>
+        <v>0.134053876087044</v>
       </c>
       <c r="G198" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H198" s="24" t="n">
         <f aca="false">IF(F198&gt;0,E198/F198,"")</f>
-        <v>-2.56206768129496</v>
+        <v>-2.55931556587244</v>
       </c>
       <c r="I198" s="24" t="n">
         <f aca="false">IF(H198="","",TDIST(ABS(H198),G198-1,2))</f>
-        <v>0.0195986379306939</v>
+        <v>0.019711872225704</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10284,21 +10284,21 @@
         <v>40</v>
       </c>
       <c r="E207" s="22" t="n">
-        <v>0.884012495422981</v>
+        <v>0.154083091943502</v>
       </c>
       <c r="F207" s="22" t="n">
-        <v>0.559978333074153</v>
+        <v>0.101473293757026</v>
       </c>
       <c r="G207" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H207" s="24" t="n">
         <f aca="false">IF(F207&gt;0,E207/F207,"")</f>
-        <v>1.57865482146417</v>
+        <v>1.51845954968653</v>
       </c>
       <c r="I207" s="24" t="n">
         <f aca="false">IF(H207="","",TDIST(ABS(H207),G207-1,2))</f>
-        <v>0.131827423337518</v>
+        <v>0.146267321389551</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10563,21 +10563,21 @@
         <v>41</v>
       </c>
       <c r="E216" s="22" t="n">
-        <v>-0.92012514868856</v>
+        <v>-0.160377515723995</v>
       </c>
       <c r="F216" s="22" t="n">
-        <v>0.41891625617395</v>
+        <v>0.0753297873846128</v>
       </c>
       <c r="G216" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H216" s="24" t="n">
         <f aca="false">IF(F216&gt;0,E216/F216,"")</f>
-        <v>-2.19644173537751</v>
+        <v>-2.12900528850762</v>
       </c>
       <c r="I216" s="24" t="n">
         <f aca="false">IF(H216="","",TDIST(ABS(H216),G216-1,2))</f>
-        <v>0.0414010294220149</v>
+        <v>0.0473165549484742</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10842,21 +10842,21 @@
         <v>43</v>
       </c>
       <c r="E225" s="22" t="n">
-        <v>-0.422953734890235</v>
+        <v>-0.422953734890236</v>
       </c>
       <c r="F225" s="22" t="n">
-        <v>0.105248480715347</v>
+        <v>0.105801996939669</v>
       </c>
       <c r="G225" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H225" s="24" t="n">
         <f aca="false">IF(F225&gt;0,E225/F225,"")</f>
-        <v>-4.01862081063336</v>
+        <v>-3.99759689915317</v>
       </c>
       <c r="I225" s="24" t="n">
         <f aca="false">IF(H225="","",TDIST(ABS(H225),G225-1,2))</f>
-        <v>0.000805714646333982</v>
+        <v>0.00084433633561776</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10938,18 +10938,18 @@
         <v>-0.240549749859148</v>
       </c>
       <c r="F228" s="22" t="n">
-        <v>0.185031889039991</v>
+        <v>0.186498673637033</v>
       </c>
       <c r="G228" s="23" t="n">
         <v>19</v>
       </c>
       <c r="H228" s="24" t="n">
         <f aca="false">IF(F228&gt;0,E228/F228,"")</f>
-        <v>-1.300044825285</v>
+        <v>-1.28982016422974</v>
       </c>
       <c r="I228" s="24" t="n">
         <f aca="false">IF(H228="","",TDIST(ABS(H228),G228-1,2))</f>
-        <v>0.209987381537066</v>
+        <v>0.213439394750894</v>
       </c>
     </row>
   </sheetData>
